--- a/PRESUPUESTO-HUAWEI-CLOUD.xlsx
+++ b/PRESUPUESTO-HUAWEI-CLOUD.xlsx
@@ -14,8 +14,10 @@
     <sheet name="LLM-MaaS" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Produccion" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Usuarios" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Escenarios" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Supuestos" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Crecimiento" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Ingesta" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Escenarios" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Supuestos" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -173,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -270,11 +272,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -969,6 +1012,600 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Escenarios de uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Mismo diseño, tres regímenes de operación</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>A · Demo y ensayos</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>B · MVP 24×7</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>C · Producción CITE</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Qué cambia</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Infraestructura Huawei</t>
+        </is>
+      </c>
+      <c r="B5" s="5">
+        <f>Detalle!$K$30-(Detalle!$K$5+Detalle!$K$8)*(1-Parametros!$B$7/Parametros!$B$6)</f>
+        <v/>
+      </c>
+      <c r="C5" s="5">
+        <f>Detalle!$K$30</f>
+        <v/>
+      </c>
+      <c r="D5" s="5">
+        <f>Produccion!$K$31</f>
+        <v/>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>A: ECS y RDS encendidos solo 80 h/mes; el almacenamiento se paga igual. C: hoja 'Produccion', costeada línea por línea (no es un multiplicador).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>LLM (ModelArts MaaS)</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>'LLM-MaaS'!$B$5*Usuarios!$B$16</f>
+        <v/>
+      </c>
+      <c r="C6" s="5">
+        <f>'LLM-MaaS'!$B$11</f>
+        <v/>
+      </c>
+      <c r="D6" s="5">
+        <f>('LLM-MaaS'!$B$5*Usuarios!$D$16+'LLM-MaaS'!$B$6*Usuarios!$D$17)*(1-'LLM-MaaS'!$B$9)</f>
+        <v/>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Volúmenes definidos en la hoja 'Usuarios'. C: 500 premium + 2.000 gratuitos, con el ahorro de cache.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Subtotal mensual (US$)</t>
+        </is>
+      </c>
+      <c r="B7" s="5">
+        <f>B5+B6</f>
+        <v/>
+      </c>
+      <c r="C7" s="5">
+        <f>C5+C6</f>
+        <v/>
+      </c>
+      <c r="D7" s="5">
+        <f>D5+D6</f>
+        <v/>
+      </c>
+      <c r="E7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Impuestos</t>
+        </is>
+      </c>
+      <c r="B8" s="5">
+        <f>B7*Parametros!$B$9</f>
+        <v/>
+      </c>
+      <c r="C8" s="5">
+        <f>C7*Parametros!$B$9</f>
+        <v/>
+      </c>
+      <c r="D8" s="5">
+        <f>D7*Parametros!$B$9</f>
+        <v/>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>0 % si se factura directo con Huawei Cloud International.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL MENSUAL (US$)</t>
+        </is>
+      </c>
+      <c r="B9" s="64">
+        <f>B7+B8</f>
+        <v/>
+      </c>
+      <c r="C9" s="64">
+        <f>C7+C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="64">
+        <f>D7+D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL MENSUAL (S/)</t>
+        </is>
+      </c>
+      <c r="B10" s="65">
+        <f>B9*Parametros!$B$8</f>
+        <v/>
+      </c>
+      <c r="C10" s="65">
+        <f>C9*Parametros!$B$8</f>
+        <v/>
+      </c>
+      <c r="D10" s="65">
+        <f>D9*Parametros!$B$8</f>
+        <v/>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Al tipo de cambio de la hoja 'Parámetros'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL ANUAL (US$)</t>
+        </is>
+      </c>
+      <c r="B11" s="64">
+        <f>B9*12</f>
+        <v/>
+      </c>
+      <c r="C11" s="64">
+        <f>C9*12</f>
+        <v/>
+      </c>
+      <c r="D11" s="64">
+        <f>D9*12</f>
+        <v/>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Sin descuento por compromiso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL ANUAL con compromiso (US$)</t>
+        </is>
+      </c>
+      <c r="B12" s="64">
+        <f>B9*12*(1-Parametros!$B$10)</f>
+        <v/>
+      </c>
+      <c r="C12" s="64">
+        <f>C9*12*(1-Parametros!$B$10)</f>
+        <v/>
+      </c>
+      <c r="D12" s="64">
+        <f>D9*12*(1-Parametros!$B$10)</f>
+        <v/>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>El descuento aplica a ECS y RDS prepagados. Aproximación conservadora: se aplica al total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Cuándo aplica cada escenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>A · Demo y ensayos — hasta el CDR del 28 de agosto. Encender ECS y RDS solo para ensayar y presentar. Es el escenario correcto para las próximas cuatro semanas y el más barato con diferencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>B · MVP 24×7 — el CITE empieza a usarlo de verdad y el servicio debe estar disponible. Es la arquitectura de INFRA-HUAWEI-CLOUD.md tal cual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>C · Producción CITE — tras la firma: fase 2 del ADR-003 (100-300 organizaciones). Base en alta disponibilidad, dos nodos de API con balanceador, NAT Gateway para el agente, CDN y WAF. Está costeado línea por línea en la hoja 'Produccion', con las palancas de recorte y lo que cuesta cada una.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>ATENCIÓN: el ADR-003 estimaba 'US$ 200-400/mes en fases 2-3' y el detalle de la hoja 'Produccion' sale por encima. La diferencia está casi entera en tres líneas que el ADR no costeó: RDS en alta disponibilidad, WAF y NAT Gateway. Conviene corregir esa cifra en el ADR antes de que el CITE la lea como compromiso.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Supuestos, fuentes y verificación</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Cada estimación, de dónde sale y cómo comprobarla</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Supuesto adoptado</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Justificación / cómo verificarlo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="57" t="inlineStr">
+        <is>
+          <t>Origen de los precios</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>Estimaciones propias con rango mín/esperado/máx</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>Huawei Cloud no publica lista de precios en HTML: solo el calculador (www.huaweicloud.com/intl/en-us/pricing/calculator.html), que es una aplicación JavaScript y no es citable ni automatizable. Se verificó también la página de precios de ECS y el PDF de facturación: explican los modos de cobro, no las tarifas. Por eso el libro trata el precio como ENTRADA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="57" t="inlineStr">
+        <is>
+          <t>Región</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>LA-Santiago</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>Es la región de Huawei Cloud más cercana a Perú (~40-60 ms desde Lima). Con la base de datos dentro de la VPC, el RTT a Postgres baja a menos de 2 ms. Exige cuenta Huawei Cloud INTERNATIONAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="57" t="inlineStr">
+        <is>
+          <t>Tamaño del ECS</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>4 vCPU / 8 GB</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>Lo fija bge-m3: ~2,3 GB residentes en RAM (documentado en adaptadores/modelo_embeddings.py); con PyTorch el proceso queda en 3,5-4,5 GB. Con 4 GB no arranca en condiciones. Sin GPU: el gate P03 se midió en CPU con p95 de 176 ms contra un techo de 2 s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="57" t="inlineStr">
+        <is>
+          <t>Tamaño del RDS</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>2 vCPU / 4 GB, nodo único, 40 GB</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>El estado de aplicación son kilobytes: ejecuciones, etapas, perfiles y el cache de respuestas LLM. 40 GB es el mínimo que admite el servicio. La alta disponibilidad primario/en espera duplica el importe y se difiere a producción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="57" t="inlineStr">
+        <is>
+          <t>Almacenamiento de datos</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>EVS 100 GB</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>Medido en el repositorio: índice LanceDB 135 MB, snapshot 66 MB, PDFs 5,3 MB. Los 100 GB son margen para el snapshot siguiente, logs y PDFs acumulados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="57" t="inlineStr">
+        <is>
+          <t>Tráfico saliente</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>30 GB al mes</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>La SPA compilada pesa 173 KB y un informe PDF ~200 KB. 30 GB es holgado para demo y piloto; conviene revisarlo si el CITE publica el acceso a sus asociados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="57" t="inlineStr">
+        <is>
+          <t>Horas de facturación</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>730 h/mes (24×7) · 80 h/mes en demo</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>730 = 365×24/12, la convención de facturación. El escenario de demo supone encender ECS y RDS solo para ensayos: el almacenamiento, la EIP y los backups se pagan igual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="57" t="inlineStr">
+        <is>
+          <t>Descuento por compromiso</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>35 %</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>Rango habitual del prepago anual (30-40 %) en ECS y RDS. VERIFICAR en el calculador cambiando el modo de facturación a Yearly/Monthly, y ajustar el parámetro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="57" t="inlineStr">
+        <is>
+          <t>Impuestos</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>Se asume facturación directa con Huawei Cloud International. Si se contrata a través de un socio peruano, poner 18 % de IGV en 'Parámetros' y todo el libro lo recoge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="57" t="inlineStr">
+        <is>
+          <t>Coste del LLM</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>US$ 0,21 por run premium</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>DATO MEDIDO el 2026-08-02 y anotado en .env.example: entre 0,19 y 0,23 por run en frío, con tres de las cinco etapas sobre glm-5.2. Es el único bloque del presupuesto que no es estimación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="57" t="inlineStr">
+        <is>
+          <t>Ahorro por cache</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>30 %</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>El envoltorio etapa() cachea por (entrada, modelo, etapa, snapshot_version). En una demo con consultas repetidas el ahorro real es mayor; 30 % es conservador para uso mixto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="57" t="inlineStr">
+        <is>
+          <t>Lo que NO está incluido</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>Dominio, desarrollo, soporte de pago</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>El plan de soporte Basic de Huawei es gratuito. El registro del dominio, las horas de implantación y cualquier licencia de terceros van fuera de este presupuesto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="57" t="inlineStr">
+        <is>
+          <t>Escenario de producción</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>Fase 2 del ADR-003, costeada línea por línea</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>La hoja 'Produccion' NO usa un multiplicador: son 18 líneas con su cantidad y su precio. Supone 100-300 organizaciones, 2 réplicas de API con balanceador, RDS en alta disponibilidad, NAT Gateway para el agente de la fase F4, CDN y WAF. Las líneas de réplica de lectura y soporte de pago están con cantidad 0: se activan poniendo 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="57" t="inlineStr">
+        <is>
+          <t>Discrepancia con el ADR-003</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>El ADR estima US$ 200-400/mes; el detalle sale por encima</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>Las tres líneas que el ADR no costeó son RDS en alta disponibilidad (duplica la base), WAF y NAT Gateway. Con las palancas de recorte de la hoja 'Produccion' se puede volver al rango del ADR, pero renunciando a cosas concretas. Conviene corregir la cifra del ADR antes de que el CITE la lea como compromiso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="57" t="inlineStr">
+        <is>
+          <t>Riesgo de subestimación</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>Peticiones de OBS y logs de LTS</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>Son las dos líneas con confianza BAJA. En volúmenes de demo son céntimos; con uso real conviene medir un mes antes de comprometer una cifra anual.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4902,286 +5539,756 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="007030A0"/>
+    <tabColor rgb="00375623"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Escenarios de uso</t>
+          <t>Crecimiento de datos a 12 meses</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mismo diseño, tres regímenes de operación</t>
+          <t>Huella por consulta MEDIDA sobre las tablas de auditoría del proyecto, no estimada</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Concepto</t>
+          <t>Huella por consulta</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>A · Demo y ensayos</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>B · MVP 24×7</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>C · Producción CITE</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Qué cambia</t>
+          <t>Origen del dato</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Infraestructura Huawei</t>
-        </is>
-      </c>
-      <c r="B5" s="5">
-        <f>Detalle!$K$30-(Detalle!$K$5+Detalle!$K$8)*(1-Parametros!$B$7/Parametros!$B$6)</f>
-        <v/>
-      </c>
-      <c r="C5" s="5">
-        <f>Detalle!$K$30</f>
-        <v/>
-      </c>
-      <c r="D5" s="5">
-        <f>Produccion!$K$31</f>
-        <v/>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>A: ECS y RDS encendidos solo 80 h/mes; el almacenamiento se paga igual. C: hoja 'Produccion', costeada línea por línea (no es un multiplicador).</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Etapa 1 · InterpretarInsumo</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>MEDIDO: 50 filas reales en etapas_ejecucion. entrada+salida en JSON.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>LLM (ModelArts MaaS)</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>'LLM-MaaS'!$B$5*Usuarios!$B$16</f>
-        <v/>
-      </c>
-      <c r="C6" s="5">
-        <f>'LLM-MaaS'!$B$11</f>
-        <v/>
-      </c>
-      <c r="D6" s="5">
-        <f>('LLM-MaaS'!$B$5*Usuarios!$D$16+'LLM-MaaS'!$B$6*Usuarios!$D$17)*(1-'LLM-MaaS'!$B$9)</f>
-        <v/>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Volúmenes definidos en la hoja 'Usuarios'. C: 500 premium + 2.000 gratuitos, con el ahorro de cache.</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Etapa 2 · MatchProductos</t>
+        </is>
+      </c>
+      <c r="B6" s="48" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>MEDIDO: 26 filas. Guarda los 30 productos con sus ingredientes.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Subtotal mensual (US$)</t>
-        </is>
-      </c>
-      <c r="B7" s="5">
-        <f>B5+B6</f>
-        <v/>
-      </c>
-      <c r="C7" s="5">
-        <f>C5+C6</f>
-        <v/>
-      </c>
-      <c r="D7" s="5">
-        <f>D5+D6</f>
-        <v/>
-      </c>
-      <c r="E7" s="7" t="inlineStr"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Etapa 2b · MapaComercial</t>
+        </is>
+      </c>
+      <c r="B7" s="48" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>MEDIDO: 10 filas. Es la etapa más pesada, 5× cualquier otra: su salida_json lleva el mapa comercial completo. Máximo observado 74 KB.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Impuestos</t>
-        </is>
-      </c>
-      <c r="B8" s="5">
-        <f>B7*Parametros!$B$9</f>
-        <v/>
-      </c>
-      <c r="C8" s="5">
-        <f>C7*Parametros!$B$9</f>
-        <v/>
-      </c>
-      <c r="D8" s="5">
-        <f>D7*Parametros!$B$9</f>
-        <v/>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>0 % si se factura directo con Huawei Cloud International.</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Etapa 3 · InsightMercado</t>
+        </is>
+      </c>
+      <c r="B8" s="48" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>MEDIDO: 50 filas.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL MENSUAL (US$)</t>
-        </is>
-      </c>
-      <c r="B9" s="48">
-        <f>B7+B8</f>
-        <v/>
-      </c>
-      <c r="C9" s="48">
-        <f>C7+C8</f>
-        <v/>
-      </c>
-      <c r="D9" s="48">
-        <f>D7+D8</f>
-        <v/>
-      </c>
-      <c r="E9" s="7" t="inlineStr"/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Etapa 4 · Formulación (premium)</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>ESTIMADO: aún no hay filas históricas de la etapa separada en S3.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL MENSUAL (S/)</t>
-        </is>
-      </c>
-      <c r="B10" s="49">
-        <f>B9*Parametros!$B$8</f>
-        <v/>
-      </c>
-      <c r="C10" s="49">
-        <f>C9*Parametros!$B$8</f>
-        <v/>
-      </c>
-      <c r="D10" s="49">
-        <f>D9*Parametros!$B$8</f>
-        <v/>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Al tipo de cambio de la hoja 'Parámetros'.</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Etapa 5 · Regulación (premium)</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>ESTIMADO: incluye el contexto del corpus regulatorio.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL ANUAL (US$)</t>
-        </is>
-      </c>
-      <c r="B11" s="48">
-        <f>B9*12</f>
-        <v/>
-      </c>
-      <c r="C11" s="48">
-        <f>C9*12</f>
-        <v/>
-      </c>
-      <c r="D11" s="48">
-        <f>D9*12</f>
-        <v/>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Sin descuento por compromiso.</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Fila de ejecución + fila de informe</t>
+        </is>
+      </c>
+      <c r="B11" s="48" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>MEDIDO: metadatos, sin JSON.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL ANUAL con compromiso (US$)</t>
-        </is>
-      </c>
-      <c r="B12" s="48">
-        <f>B9*12*(1-Parametros!$B$10)</f>
-        <v/>
-      </c>
-      <c r="C12" s="48">
-        <f>C9*12*(1-Parametros!$B$10)</f>
-        <v/>
-      </c>
-      <c r="D12" s="48">
-        <f>D9*12*(1-Parametros!$B$10)</f>
-        <v/>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>El descuento aplica a ECS y RDS prepagados. Aproximación conservadora: se aplica al total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>Cuándo aplica cada escenario</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>A · Demo y ensayos — hasta el CDR del 28 de agosto. Encender ECS y RDS solo para ensayar y presentar. Es el escenario correcto para las próximas cuatro semanas y el más barato con diferencia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>B · MVP 24×7 — el CITE empieza a usarlo de verdad y el servicio debe estar disponible. Es la arquitectura de INFRA-HUAWEI-CLOUD.md tal cual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>C · Producción CITE — tras la firma: fase 2 del ADR-003 (100-300 organizaciones). Base en alta disponibilidad, dos nodos de API con balanceador, NAT Gateway para el agente, CDN y WAF. Está costeado línea por línea en la hoja 'Produccion', con las palancas de recorte y lo que cuesta cada una.</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Cache LLM por llamada nueva</t>
+        </is>
+      </c>
+      <c r="B12" s="48" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>MEDIDO: 60 filas de cache_llm, 129,7 KB en total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>PDF del informe</t>
+        </is>
+      </c>
+      <c r="B13" s="48" t="n">
+        <v>26</v>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>MEDIDO: 216 PDFs reales en informes/, 5,5 MB en total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL por consulta PREMIUM (6 etapas)</t>
+        </is>
+      </c>
+      <c r="B15" s="49">
+        <f>B5+B6+B7+B8+B9+B10+B11+B12*4*(1-'LLM-MaaS'!$B$9)</f>
+        <v/>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>4 etapas con LLM; el cache evita guardar el 30 % de las llamadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL por consulta GRATUITA (4 etapas)</t>
+        </is>
+      </c>
+      <c r="B16" s="49">
+        <f>B5+B6+B7+B8+B11+B12*2*(1-'LLM-MaaS'!$B$9)</f>
+        <v/>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>El paywall corta antes de las etapas 4 y 5.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>ATENCIÓN: el ADR-003 estimaba 'US$ 200-400/mes en fases 2-3' y el detalle de la hoja 'Produccion' sale por encima. La diferencia está casi entera en tres líneas que el ADR no costeó: RDS en alta disponibilidad, WAF y NAT Gateway. Conviene corregir esa cifra en el ADR antes de que el CITE la lea como compromiso.</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Crecimiento por snapshot de datos</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Productos por snapshot</t>
+        </is>
+      </c>
+      <c r="B19" s="50" t="n">
+        <v>29054</v>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>MEDIDO: los 5 insumos piloto del snapshot 2026-07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KB por producto (JSON + vector)</t>
+        </is>
+      </c>
+      <c r="B20" s="48" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>MEDIDO: 66 MB de JSON + 135 MB de índice LanceDB ÷ 29.054 productos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Tamaño de un snapshot (MB)</t>
+        </is>
+      </c>
+      <c r="B21" s="51">
+        <f>B19*B20/1024</f>
+        <v/>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>Calculado. El snapshot actual pesa ~201 MB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Snapshots publicados al año</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>EDITAR. Trimestral es lo razonable; mensual multiplica por 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>¿Se conservan los anteriores?</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>El versionado de OBS los guarda: es el respaldo de los datasets (H8 del ADR).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>ACUMULADO MES A MES</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>B · RDS (GB)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>B · OBS (GB)</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>C · RDS (GB)</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>C · OBS (GB)</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>C · % del RDS presupuestado</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>C · % del OBS presupuestado</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="37">
+        <f>A28*(Usuarios!$C$16*$B$15+Usuarios!$C$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="C28" s="37">
+        <f>2.3+A28*(Usuarios!$C$18*$B$13)/1048576+(1+INT(A28*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="D28" s="37">
+        <f>A28*(Usuarios!$D$16*$B$15+Usuarios!$D$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="E28" s="37">
+        <f>2.3+A28*(Usuarios!$D$18*$B$13)/1048576+(1+INT(A28*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="F28" s="53">
+        <f>D28/Detalle!$E$9</f>
+        <v/>
+      </c>
+      <c r="G28" s="53">
+        <f>E28/Detalle!$E$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="37">
+        <f>A29*(Usuarios!$C$16*$B$15+Usuarios!$C$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="C29" s="37">
+        <f>2.3+A29*(Usuarios!$C$18*$B$13)/1048576+(1+INT(A29*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="D29" s="37">
+        <f>A29*(Usuarios!$D$16*$B$15+Usuarios!$D$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="E29" s="37">
+        <f>2.3+A29*(Usuarios!$D$18*$B$13)/1048576+(1+INT(A29*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="F29" s="53">
+        <f>D29/Detalle!$E$9</f>
+        <v/>
+      </c>
+      <c r="G29" s="53">
+        <f>E29/Detalle!$E$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="37">
+        <f>A30*(Usuarios!$C$16*$B$15+Usuarios!$C$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="C30" s="37">
+        <f>2.3+A30*(Usuarios!$C$18*$B$13)/1048576+(1+INT(A30*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="D30" s="37">
+        <f>A30*(Usuarios!$D$16*$B$15+Usuarios!$D$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="E30" s="37">
+        <f>2.3+A30*(Usuarios!$D$18*$B$13)/1048576+(1+INT(A30*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="F30" s="53">
+        <f>D30/Detalle!$E$9</f>
+        <v/>
+      </c>
+      <c r="G30" s="53">
+        <f>E30/Detalle!$E$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="37">
+        <f>A31*(Usuarios!$C$16*$B$15+Usuarios!$C$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="C31" s="37">
+        <f>2.3+A31*(Usuarios!$C$18*$B$13)/1048576+(1+INT(A31*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="D31" s="37">
+        <f>A31*(Usuarios!$D$16*$B$15+Usuarios!$D$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="E31" s="37">
+        <f>2.3+A31*(Usuarios!$D$18*$B$13)/1048576+(1+INT(A31*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="F31" s="53">
+        <f>D31/Detalle!$E$9</f>
+        <v/>
+      </c>
+      <c r="G31" s="53">
+        <f>E31/Detalle!$E$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="37">
+        <f>A32*(Usuarios!$C$16*$B$15+Usuarios!$C$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="C32" s="37">
+        <f>2.3+A32*(Usuarios!$C$18*$B$13)/1048576+(1+INT(A32*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="D32" s="37">
+        <f>A32*(Usuarios!$D$16*$B$15+Usuarios!$D$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="E32" s="37">
+        <f>2.3+A32*(Usuarios!$D$18*$B$13)/1048576+(1+INT(A32*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="F32" s="53">
+        <f>D32/Detalle!$E$9</f>
+        <v/>
+      </c>
+      <c r="G32" s="53">
+        <f>E32/Detalle!$E$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="37">
+        <f>A33*(Usuarios!$C$16*$B$15+Usuarios!$C$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="C33" s="37">
+        <f>2.3+A33*(Usuarios!$C$18*$B$13)/1048576+(1+INT(A33*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="D33" s="37">
+        <f>A33*(Usuarios!$D$16*$B$15+Usuarios!$D$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="E33" s="37">
+        <f>2.3+A33*(Usuarios!$D$18*$B$13)/1048576+(1+INT(A33*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="F33" s="53">
+        <f>D33/Detalle!$E$9</f>
+        <v/>
+      </c>
+      <c r="G33" s="53">
+        <f>E33/Detalle!$E$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="37">
+        <f>A34*(Usuarios!$C$16*$B$15+Usuarios!$C$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="C34" s="37">
+        <f>2.3+A34*(Usuarios!$C$18*$B$13)/1048576+(1+INT(A34*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="D34" s="37">
+        <f>A34*(Usuarios!$D$16*$B$15+Usuarios!$D$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="E34" s="37">
+        <f>2.3+A34*(Usuarios!$D$18*$B$13)/1048576+(1+INT(A34*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="F34" s="53">
+        <f>D34/Detalle!$E$9</f>
+        <v/>
+      </c>
+      <c r="G34" s="53">
+        <f>E34/Detalle!$E$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" s="37">
+        <f>A35*(Usuarios!$C$16*$B$15+Usuarios!$C$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="C35" s="37">
+        <f>2.3+A35*(Usuarios!$C$18*$B$13)/1048576+(1+INT(A35*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="D35" s="37">
+        <f>A35*(Usuarios!$D$16*$B$15+Usuarios!$D$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="E35" s="37">
+        <f>2.3+A35*(Usuarios!$D$18*$B$13)/1048576+(1+INT(A35*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="F35" s="53">
+        <f>D35/Detalle!$E$9</f>
+        <v/>
+      </c>
+      <c r="G35" s="53">
+        <f>E35/Detalle!$E$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="52" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" s="37">
+        <f>A36*(Usuarios!$C$16*$B$15+Usuarios!$C$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="C36" s="37">
+        <f>2.3+A36*(Usuarios!$C$18*$B$13)/1048576+(1+INT(A36*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="D36" s="37">
+        <f>A36*(Usuarios!$D$16*$B$15+Usuarios!$D$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="E36" s="37">
+        <f>2.3+A36*(Usuarios!$D$18*$B$13)/1048576+(1+INT(A36*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="F36" s="53">
+        <f>D36/Detalle!$E$9</f>
+        <v/>
+      </c>
+      <c r="G36" s="53">
+        <f>E36/Detalle!$E$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="52" t="n">
+        <v>10</v>
+      </c>
+      <c r="B37" s="37">
+        <f>A37*(Usuarios!$C$16*$B$15+Usuarios!$C$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="C37" s="37">
+        <f>2.3+A37*(Usuarios!$C$18*$B$13)/1048576+(1+INT(A37*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="D37" s="37">
+        <f>A37*(Usuarios!$D$16*$B$15+Usuarios!$D$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="E37" s="37">
+        <f>2.3+A37*(Usuarios!$D$18*$B$13)/1048576+(1+INT(A37*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="F37" s="53">
+        <f>D37/Detalle!$E$9</f>
+        <v/>
+      </c>
+      <c r="G37" s="53">
+        <f>E37/Detalle!$E$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="52" t="n">
+        <v>11</v>
+      </c>
+      <c r="B38" s="37">
+        <f>A38*(Usuarios!$C$16*$B$15+Usuarios!$C$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="C38" s="37">
+        <f>2.3+A38*(Usuarios!$C$18*$B$13)/1048576+(1+INT(A38*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>A38*(Usuarios!$D$16*$B$15+Usuarios!$D$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="E38" s="37">
+        <f>2.3+A38*(Usuarios!$D$18*$B$13)/1048576+(1+INT(A38*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="F38" s="53">
+        <f>D38/Detalle!$E$9</f>
+        <v/>
+      </c>
+      <c r="G38" s="53">
+        <f>E38/Detalle!$E$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="54" t="n">
+        <v>12</v>
+      </c>
+      <c r="B39" s="55">
+        <f>A39*(Usuarios!$C$16*$B$15+Usuarios!$C$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="C39" s="55">
+        <f>2.3+A39*(Usuarios!$C$18*$B$13)/1048576+(1+INT(A39*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="D39" s="55">
+        <f>A39*(Usuarios!$D$16*$B$15+Usuarios!$D$17*$B$16)/1048576</f>
+        <v/>
+      </c>
+      <c r="E39" s="55">
+        <f>2.3+A39*(Usuarios!$D$18*$B$13)/1048576+(1+INT(A39*$B$22/12))*$B$21/1024</f>
+        <v/>
+      </c>
+      <c r="F39" s="56">
+        <f>D39/Detalle!$E$9</f>
+        <v/>
+      </c>
+      <c r="G39" s="56">
+        <f>E39/Detalle!$E$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="43" t="inlineStr">
+        <is>
+          <t>Veredicto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="48" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>1. NADA se desborda en el primer año. Con el escenario C —250 usuarios activos, 2.500 consultas al mes— el RDS llega al mes 12 con unos 3 GB de los 40 GB contratados (7 %) y el OBS con unos 4 GB de los 20 GB (20 %). El almacenamiento presupuestado da para más de una década al ritmo del escenario C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="48" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>2. Lo que hace crecer la plataforma NO son los usuarios: son los snapshots. Un snapshot de los 5 insumos piloto pesa ~201 MB, y con versionado de OBS los anteriores se conservan. Pasar de 5 a 20 insumos multiplica por 4 el tamaño de CADA snapshot (~800 MB), y publicar mensualmente en vez de trimestralmente lo multiplica por 3 otra vez. Ahí sí hay que rehacer la cuenta: son los dos únicos parámetros que mueven la aguja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="48" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>3. Hallazgo: la etapa 2b ocupa 59 KB por consulta, cinco veces más que cualquier otra etapa, porque guarda el mapa comercial completo en salida_json. Hoy es irrelevante en volumen, pero es la línea que crecería si el mapa pasara de 30 a 200 productos. Si algún día molesta, la solución es guardar los identificadores y reconstruir el mapa desde el catálogo, no comprimir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="48" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>4. Hallazgo: cache_llm no tiene TTL ni purga. La clave incluye snapshot_version, así que las entradas viejas quedan lógicamente invalidadas pero las filas se acumulan. A 2,2 KB por fila no es un problema de espacio en años; conviene saberlo antes de que alguien lo descubra buscando otra cosa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="48" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>5. Lo que sí conviene automatizar desde el día 1: purgar los PDFs locales de /data/informes tras subirlos a OBS. Son 26 KB cada uno, pero el disco es el único almacén sin política de retención.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
+  <mergeCells count="5">
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A46:G46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5190,305 +6297,948 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="001F6F8B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="88" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="56" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supuestos, fuentes y verificación</t>
+          <t>Ingesta de datos — lo que el software traga en cada ciclo</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cada estimación, de dónde sale y cómo comprobarla</t>
+          <t>Tiempos y volúmenes MEDIDOS en los logs del ETL de la Semana 2 (datasets/2026-07/)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Tema</t>
+          <t>Fuente</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Supuesto adoptado</t>
+          <t>Método</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Justificación / cómo verificarlo</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="50" t="inlineStr">
-        <is>
-          <t>Origen de los precios</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>Estimaciones propias con rango mín/esperado/máx</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>Huawei Cloud no publica lista de precios en HTML: solo el calculador (www.huaweicloud.com/intl/en-us/pricing/calculator.html), que es una aplicación JavaScript y no es citable ni automatizable. Se verificó también la página de precios de ECS y el PDF de facturación: explican los modos de cobro, no las tarifas. Por eso el libro trata el precio como ENTRADA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="50" t="inlineStr">
-        <is>
-          <t>Región</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>LA-Santiago</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>Es la región de Huawei Cloud más cercana a Perú (~40-60 ms desde Lima). Con la base de datos dentro de la VPC, el RTT a Postgres baja a menos de 2 ms. Exige cuenta Huawei Cloud INTERNATIONAL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="50" t="inlineStr">
-        <is>
-          <t>Tamaño del ECS</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>4 vCPU / 8 GB</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>Lo fija bge-m3: ~2,3 GB residentes en RAM (documentado en adaptadores/modelo_embeddings.py); con PyTorch el proceso queda en 3,5-4,5 GB. Con 4 GB no arranca en condiciones. Sin GPU: el gate P03 se midió en CPU con p95 de 176 ms contra un techo de 2 s.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="50" t="inlineStr">
-        <is>
-          <t>Tamaño del RDS</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>2 vCPU / 4 GB, nodo único, 40 GB</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>El estado de aplicación son kilobytes: ejecuciones, etapas, perfiles y el cache de respuestas LLM. 40 GB es el mínimo que admite el servicio. La alta disponibilidad primario/en espera duplica el importe y se difiere a producción.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="50" t="inlineStr">
-        <is>
-          <t>Almacenamiento de datos</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>EVS 100 GB</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>Medido en el repositorio: índice LanceDB 135 MB, snapshot 66 MB, PDFs 5,3 MB. Los 100 GB son margen para el snapshot siguiente, logs y PDFs acumulados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="50" t="inlineStr">
-        <is>
-          <t>Tráfico saliente</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>30 GB al mes</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>La SPA compilada pesa 173 KB y un informe PDF ~200 KB. 30 GB es holgado para demo y piloto; conviene revisarlo si el CITE publica el acceso a sus asociados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="50" t="inlineStr">
-        <is>
-          <t>Horas de facturación</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>730 h/mes (24×7) · 80 h/mes en demo</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>730 = 365×24/12, la convención de facturación. El escenario de demo supone encender ECS y RDS solo para ensayos: el almacenamiento, la EIP y los backups se pagan igual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="50" t="inlineStr">
-        <is>
-          <t>Descuento por compromiso</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>35 %</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>Rango habitual del prepago anual (30-40 %) en ECS y RDS. VERIFICAR en el calculador cambiando el modo de facturación a Yearly/Monthly, y ajustar el parámetro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="50" t="inlineStr">
-        <is>
-          <t>Impuestos</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>0 %</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>Se asume facturación directa con Huawei Cloud International. Si se contrata a través de un socio peruano, poner 18 % de IGV en 'Parámetros' y todo el libro lo recoge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="50" t="inlineStr">
-        <is>
-          <t>Coste del LLM</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>US$ 0,21 por run premium</t>
-        </is>
+          <t>Descargado</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Filas leídas</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Registros retenidos</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Tiempo medido</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Frecuencia</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="57" t="inlineStr">
+        <is>
+          <t>Open Food Facts</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Export masivo CSV.gz</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>2,0 GB</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>4.532.767</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
+        <is>
+          <t>28.236</t>
+        </is>
+      </c>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>10 min 29 s</t>
+        </is>
+      </c>
+      <c r="G5" s="28" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>MEDIDO en etl_off_bulk.log: descarga 2 min 30 s (13 MB/s) + filtrado 7 min 59 s. Es el 97 % de toda la ingesta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="57" t="inlineStr">
+        <is>
+          <t>USDA Branded</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>API por insumo</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>~15 MB</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>990 → 818 tras dedup</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>5-15 min</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>Requiere USDA_API_KEY. Filtra dataType=Branded y trae modifiedDate como fecha real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="57" t="inlineStr">
+        <is>
+          <t>eCFR Title 21</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>API pública</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>~5 MB</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>702 documentos</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>~10 min</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>99.333 palabras. NO cubre los insumos piloto: es normativa de aditivos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="57" t="inlineStr">
+        <is>
+          <t>DIGESA</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Descarga de PDF + extracción</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>~20 MB</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>32 documentos</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>~30 min</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>6.602 palabras. 5 PDFs quedaron fuera por ser escaneos. El sitio devuelve 403 si se piden páginas seguidas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="57" t="inlineStr">
+        <is>
+          <t>Open Prices</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>API por código de barras</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>&lt;1 MB</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>Por medir (sonda de S4)</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
+        <is>
+          <t>~5 min</t>
+        </is>
+      </c>
+      <c r="G9" s="28" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>Aún no integrada. La sonda del TIER 1 de S4 mide primero la cobertura real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="57" t="inlineStr">
+        <is>
+          <t>Agente web (fase F4)</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>Tavily + extracción</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>A cuarentena con TTL</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>Por run</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>Continua</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>No entra en el MVP. Ingesta continua y de bajo volumen, con grounding check antes de promover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>LO QUE ESTO SIGNIFICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Métrica del ciclo</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Cómo sale</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Ratio de retención (filas)</t>
+        </is>
+      </c>
+      <c r="B14" s="58" t="n">
+        <v>0.0062</v>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>DATO MEDIDO el 2026-08-02 y anotado en .env.example: entre 0,19 y 0,23 por run en frío, con tres de las cinco etapas sobre glm-5.2. Es el único bloque del presupuesto que no es estimación.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="50" t="inlineStr">
-        <is>
-          <t>Ahorro por cache</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>30 %</t>
-        </is>
+          <t>28.236 de 4.532.767 filas de OFF. Se descarta el 99,4 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Ratio de retención (bytes)</t>
+        </is>
+      </c>
+      <c r="B15" s="58" t="n">
+        <v>0.033</v>
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>El envoltorio etapa() cachea por (entrada, modelo, etapa, snapshot_version). En una demo con consultas repetidas el ahorro real es mayor; 30 % es conservador para uso mixto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="50" t="inlineStr">
-        <is>
-          <t>Lo que NO está incluido</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>Dominio, desarrollo, soporte de pago</t>
-        </is>
+          <t>66 MB de JSON retenidos de 2,0 GB descargados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Descarga por ciclo (GB)</t>
+        </is>
+      </c>
+      <c r="B16" s="48" t="n">
+        <v>2.05</v>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>El plan de soporte Basic de Huawei es gratuito. El registro del dominio, las horas de implantación y cualquier licencia de terceros van fuera de este presupuesto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="46" customHeight="1">
-      <c r="A17" s="50" t="inlineStr">
-        <is>
-          <t>Escenario de producción</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>Fase 2 del ADR-003, costeada línea por línea</t>
-        </is>
+          <t>OFF domina; el resto de fuentes son ruido a su lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Tiempo de ingesta por ciclo (min)</t>
+        </is>
+      </c>
+      <c r="B17" s="48" t="n">
+        <v>70</v>
       </c>
       <c r="C17" s="21" t="inlineStr">
         <is>
-          <t>La hoja 'Produccion' NO usa un multiplicador: son 18 líneas con su cantidad y su precio. Supone 100-300 organizaciones, 2 réplicas de API con balanceador, RDS en alta disponibilidad, NAT Gateway para el agente de la fase F4, CDN y WAF. Las líneas de réplica de lectura y soporte de pago están con cantidad 0: se activan poniendo 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="46" customHeight="1">
-      <c r="A18" s="50" t="inlineStr">
-        <is>
-          <t>Discrepancia con el ADR-003</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>El ADR estima US$ 200-400/mes; el detalle sale por encima</t>
-        </is>
+          <t>OFF 10,5 + USDA 15 + eCFR 10 + DIGESA 30, con margen. Sin embeddings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Disco temporal necesario (GB)</t>
+        </is>
+      </c>
+      <c r="B18" s="48" t="n">
+        <v>5</v>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Las tres líneas que el ADR no costeó son RDS en alta disponibilidad (duplica la base), WAF y NAT Gateway. Con las palancas de recorte de la hoja 'Produccion' se puede volver al rango del ADR, pero renunciando a cosas concretas. Conviene corregir la cifra del ADR antes de que el CITE la lea como compromiso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="46" customHeight="1">
-      <c r="A19" s="50" t="inlineStr">
-        <is>
-          <t>Riesgo de subestimación</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>Peticiones de OBS y logs de LTS</t>
-        </is>
+          <t>El .gz de 2 GB más margen. Se lee en streaming: no se descomprime a disco.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Coste del tráfico de ENTRADA</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Son las dos líneas con confianza BAJA. En volúmenes de demo son céntimos; con uso real conviene medir un mes antes de comprometer una cifra anual.</t>
+          <t>El ingress no se cobra en Huawei Cloud. Descargar 2 GB por ciclo es gratis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Snapshot resultante (MB)</t>
+        </is>
+      </c>
+      <c r="B20" s="48" t="n">
+        <v>201</v>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>66 MB de JSON + 135 MB de índice vectorial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>EL CUELLO DE LA INGESTA NO ES LA DESCARGA: SON LOS EMBEDDINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Modo de indexación</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Velocidad medida</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>29.054 productos</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>116.000 productos (20 insumos)</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="57" t="inlineStr">
+        <is>
+          <t>GPU (RTX 4060, batch 128)</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>100-200 prod/s</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>15-30 min</t>
+        </is>
+      </c>
+      <c r="D24" s="28" t="inlineStr">
+        <is>
+          <t>1-2 horas</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>MEDIDO en TIER 4 de la Semana 2. Es la máquina de desarrollo, no la nube.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="57" t="inlineStr">
+        <is>
+          <t>CPU (el ECS de producción)</t>
+        </is>
+      </c>
+      <c r="B25" s="28" t="inlineStr">
+        <is>
+          <t>4-5 prod/s</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>2-3 horas</t>
+        </is>
+      </c>
+      <c r="D25" s="28" t="inlineStr">
+        <is>
+          <t>7-8 horas</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>El ECS NO tiene GPU. Reindexar entero en producción bloquea el nodo y compite con la API.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="57" t="inlineStr">
+        <is>
+          <t>Incremental (solo lo nuevo)</t>
+        </is>
+      </c>
+      <c r="B26" s="28" t="inlineStr">
+        <is>
+          <t>80 prod/s en GPU</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="inlineStr">
+        <is>
+          <t>10,2 s para 818 nuevos</t>
+        </is>
+      </c>
+      <c r="D26" s="28" t="inlineStr">
+        <is>
+          <t>Proporcional al delta</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>MEDIDO en TIER 7: etl/indexar_incremental.py compara por id y embebe solo lo que falta. Es el modo normal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>¿DÓNDE CORRE LA INGESTA? (hoy: en un portátil)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Opción</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Coste anual</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Ventaja</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Inconveniente</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Veredicto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="44" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>A · Portátil con RTX 4060 y subida a OBS</t>
+        </is>
+      </c>
+      <c r="B30" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>Coste cero y es lo que ya funciona: TIER 4 y TIER 7 se hicieron así.</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>La reproducibilidad depende de una máquina personal. Si esa máquina no está, no hay snapshot nuevo.</t>
+        </is>
+      </c>
+      <c r="E30" s="57" t="inlineStr">
+        <is>
+          <t>Vale para el MVP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="44" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>B · En el ECS de producción, con CPU</t>
+        </is>
+      </c>
+      <c r="B31" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>Todo en la nube, sin piezas fuera del despliegue.</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>2-3 h de CPU al 100 % por ciclo completo compitiendo con la API: la latencia p95 se va al techo.</t>
+        </is>
+      </c>
+      <c r="E31" s="57" t="inlineStr">
+        <is>
+          <t>Solo en modo incremental</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="44" customHeight="1">
+      <c r="A32" s="59" t="inlineStr">
+        <is>
+          <t>C · ECS con GPU encendido por horas</t>
+        </is>
+      </c>
+      <c r="B32" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="C32" s="60" t="inlineStr">
+        <is>
+          <t>1 hora por trimestre a ~US$ 1-2/h. Reproducible, en la nube y no toca el nodo de producción.</t>
+        </is>
+      </c>
+      <c r="D32" s="60" t="inlineStr">
+        <is>
+          <t>Una pieza más que aprovisionar, aunque sea efímera.</t>
+        </is>
+      </c>
+      <c r="E32" s="61" t="inlineStr">
+        <is>
+          <t>RECOMENDADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="44" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>D · Nodo dedicado con GPU 24×7</t>
+        </is>
+      </c>
+      <c r="B33" s="34" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>Disponible siempre.</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>Se paga el 100 % del mes para usarlo 4 horas al año.</t>
+        </is>
+      </c>
+      <c r="E33" s="57" t="inlineStr">
+        <is>
+          <t>Descartada</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>PROYECCIÓN ANUAL DE INGESTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>5 insumos (hoy)</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>20 insumos</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Ciclos al año</t>
+        </is>
+      </c>
+      <c r="B37" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>EDITAR. Trimestral. Mensual multiplica todo por 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>GB descargados al año</t>
+        </is>
+      </c>
+      <c r="B38" s="62">
+        <f>B37*2.05</f>
+        <v/>
+      </c>
+      <c r="C38" s="62">
+        <f>C37*2.05*1.0</f>
+        <v/>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>El export de OFF es el mismo tamaño: no depende de cuántos insumos se filtren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Millones de filas procesadas</t>
+        </is>
+      </c>
+      <c r="B39" s="62">
+        <f>B37*4.53</f>
+        <v/>
+      </c>
+      <c r="C39" s="62">
+        <f>C37*4.53</f>
+        <v/>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Se lee el export entero en las dos hipótesis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Productos retenidos por ciclo</t>
+        </is>
+      </c>
+      <c r="B40" s="23" t="n">
+        <v>29054</v>
+      </c>
+      <c r="C40" s="23" t="n">
+        <v>116000</v>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>El filtro es lo único que cambia al añadir insumos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>MB de snapshot por ciclo</t>
+        </is>
+      </c>
+      <c r="B41" s="62">
+        <f>B40*7.1/1024</f>
+        <v/>
+      </c>
+      <c r="C41" s="62">
+        <f>C40*7.1/1024</f>
+        <v/>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>7,1 KB por producto entre JSON y vector (medido).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>GB acumulados al año en OBS</t>
+        </is>
+      </c>
+      <c r="B42" s="62">
+        <f>B37*B41/1024</f>
+        <v/>
+      </c>
+      <c r="C42" s="62">
+        <f>C37*C41/1024</f>
+        <v/>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Con versionado: los snapshots antiguos se conservan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Horas de indexación al año (GPU)</t>
+        </is>
+      </c>
+      <c r="B43" s="62">
+        <f>B37*B40/150/3600</f>
+        <v/>
+      </c>
+      <c r="C43" s="62">
+        <f>C37*C40/150/3600</f>
+        <v/>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>A 150 prod/s. Reindexado COMPLETO; en incremental es una fracción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Horas de indexación al año (CPU)</t>
+        </is>
+      </c>
+      <c r="B44" s="62">
+        <f>B37*B40/4.5/3600</f>
+        <v/>
+      </c>
+      <c r="C44" s="62">
+        <f>C37*C40/4.5/3600</f>
+        <v/>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>A 4,5 prod/s. Es lo que costaría hacerlo en el ECS de producción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Coste de la ingesta al año</t>
+        </is>
+      </c>
+      <c r="B45" s="63">
+        <f>$B$32</f>
+        <v/>
+      </c>
+      <c r="C45" s="63">
+        <f>$B$32*2</f>
+        <v/>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Opción C: ECS con GPU por horas. El tráfico de entrada es gratis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="43" t="inlineStr">
+        <is>
+          <t>Tres conclusiones</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="46" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>1. La ingesta NO es un problema de almacenamiento ni de red: es un problema de CPU una vez por trimestre. Se descargan 2 GB y se retienen 66 MB (el 3 %); el tráfico de entrada no se cobra. Lo caro es convertir 29.054 productos en vectores: 15-30 min con GPU, 2-3 horas sin ella.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="46" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>2. El plan original sobreestimaba esta tarea. PLAN-MVP-v2 §10 la llamaba 'la tarea con más varianza del plan (~9 GB de descarga)' y recomendaba arrancarla el día 1. La medición real: 2,0 GB y 10 minutos y medio de principio a fin. El riesgo estaba en otro sitio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="46" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>3. Hoy la ingesta vive en un portátil con GPU. Para el CDR está bien y no hay que tocarlo, pero es la única pieza del sistema que no está en la nube ni es reproducible por otra persona. La salida barata es un ECS con GPU encendido una hora por trimestre: unos US$ 8 al año.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A48:E48"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>